--- a/Vickers-stage2-model4.xlsx
+++ b/Vickers-stage2-model4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kalaivickers/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFA4F3E-7C86-E549-8377-71423293DD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D571B9-D026-044D-B1BB-8B4418151C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14580" yWindow="760" windowWidth="19980" windowHeight="20180" activeTab="3" xr2:uid="{4E003E87-490A-4B41-B27B-59CE5DEAFF18}"/>
+    <workbookView xWindow="13600" yWindow="760" windowWidth="20960" windowHeight="20180" activeTab="3" xr2:uid="{4E003E87-490A-4B41-B27B-59CE5DEAFF18}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -288,6 +288,1387 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Hedge Strategy Comparison (±5% S_T)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>S_T</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$A$2:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.1138749999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1250137499999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1362638875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1476265263750001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1591027916387502</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1706938195551377</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1824007577506892</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1942247653281961</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2061670129814781</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.218228683111293</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.230410969942406</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NoHedge</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$B$2:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>8911000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9000110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9090111.0999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9181012.2110000011</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9272822.3331100009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9365550.5564411022</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9459206.0620055143</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9553798.1226255689</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9649336.103851825</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9745829.4648903441</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9843287.7595392484</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Forward</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$C$2:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8712000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8712000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MoneyMarket</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9453858.2677165363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PutNet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$E$2:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>8751000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8840110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8930111.0999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9021012.2110000011</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9112822.3331100009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9205550.5564411022</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9299206.0620055143</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9393798.1226255689</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9489336.103851825</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9585829.4648903441</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9683287.7595392484</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sensitivity!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CallNet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sensitivity!$F$2:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>8751000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8840110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8930111.0999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9021012.2110000011</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9112822.3331100009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9205550.5564411022</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9299206.0620055143</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9393798.1226255689</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9489336.103851825</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9585829.4648903441</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9683287.7595392484</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-6A5E-464F-BCA6-E5E4A6920CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2130047615"/>
+        <c:axId val="1975300143"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2130047615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1975300143"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1975300143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD Proceeds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2130047615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B49520D-D194-860D-BD0A-00FBBF96E99A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -764,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF15012-D811-4C4A-B425-051002E06023}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -800,15 +2181,15 @@
         <v>8911000</v>
       </c>
       <c r="C2">
-        <f xml:space="preserve"> FC_AMT * F0_in</f>
+        <f t="shared" ref="C2:C12" si="0" xml:space="preserve"> FC_AMT * F0_in</f>
         <v>8712000</v>
       </c>
       <c r="D2">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E10" si="0" xml:space="preserve"> FC_AMT * MAX(A2, K_PUT) - PREM_PUT * FC_AMT</f>
+        <f t="shared" ref="E2" si="1" xml:space="preserve"> FC_AMT * MAX(A2, K_PUT) - PREM_PUT * FC_AMT</f>
         <v>8751000</v>
       </c>
       <c r="F2" cm="1">
@@ -825,16 +2206,16 @@
         <f t="array" ref="B3" xml:space="preserve"> FC_AMT * A3</f>
         <v>9000110</v>
       </c>
-      <c r="C3" cm="1">
-        <f t="array" ref="C3" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C3">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D3">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E3:E12" si="2" xml:space="preserve"> FC_AMT * MAX(A3, K_PUT) - PREM_PUT * FC_AMT</f>
         <v>8840110</v>
       </c>
       <c r="F3" cm="1">
@@ -844,23 +2225,23 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A10" si="1" xml:space="preserve"> $A3 * 1.01</f>
+        <f t="shared" ref="A4:A12" si="3" xml:space="preserve"> $A3 * 1.01</f>
         <v>1.1362638875</v>
       </c>
       <c r="B4" cm="1">
         <f t="array" ref="B4" xml:space="preserve"> FC_AMT * A4</f>
         <v>9090111.0999999996</v>
       </c>
-      <c r="C4" cm="1">
-        <f t="array" ref="C4" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C4">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D4">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8930111.0999999996</v>
       </c>
       <c r="F4" cm="1">
@@ -870,23 +2251,23 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1476265263750001</v>
       </c>
       <c r="B5" cm="1">
         <f t="array" ref="B5" xml:space="preserve"> FC_AMT * A5</f>
         <v>9181012.2110000011</v>
       </c>
-      <c r="C5" cm="1">
-        <f t="array" ref="C5" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C5">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D5">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9021012.2110000011</v>
       </c>
       <c r="F5" cm="1">
@@ -896,23 +2277,23 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1591027916387502</v>
       </c>
       <c r="B6" cm="1">
         <f t="array" ref="B6" xml:space="preserve"> FC_AMT * A6</f>
         <v>9272822.3331100009</v>
       </c>
-      <c r="C6" cm="1">
-        <f t="array" ref="C6" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C6">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D6">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9112822.3331100009</v>
       </c>
       <c r="F6" cm="1">
@@ -922,23 +2303,23 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1706938195551377</v>
       </c>
       <c r="B7" cm="1">
         <f t="array" ref="B7" xml:space="preserve"> FC_AMT * A7</f>
         <v>9365550.5564411022</v>
       </c>
-      <c r="C7" cm="1">
-        <f t="array" ref="C7" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C7">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D7">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9205550.5564411022</v>
       </c>
       <c r="F7" cm="1">
@@ -948,23 +2329,23 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1824007577506892</v>
       </c>
       <c r="B8" cm="1">
         <f t="array" ref="B8" xml:space="preserve"> FC_AMT * A8</f>
         <v>9459206.0620055143</v>
       </c>
-      <c r="C8" cm="1">
-        <f t="array" ref="C8" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C8">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D8">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9299206.0620055143</v>
       </c>
       <c r="F8" cm="1">
@@ -974,23 +2355,23 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1942247653281961</v>
       </c>
       <c r="B9" cm="1">
         <f t="array" ref="B9" xml:space="preserve"> FC_AMT * A9</f>
         <v>9553798.1226255689</v>
       </c>
-      <c r="C9" cm="1">
-        <f t="array" ref="C9" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C9">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D9">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9393798.1226255689</v>
       </c>
       <c r="F9" cm="1">
@@ -1000,23 +2381,23 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2061670129814781</v>
       </c>
       <c r="B10" cm="1">
         <f t="array" ref="B10" xml:space="preserve"> FC_AMT * A10</f>
         <v>9649336.103851825</v>
       </c>
-      <c r="C10" cm="1">
-        <f t="array" ref="C10" xml:space="preserve"> FC_AMT * F0_in</f>
+      <c r="C10">
+        <f t="shared" si="0"/>
         <v>8712000</v>
       </c>
       <c r="D10">
-        <f xml:space="preserve"> Calculations!$C$6</f>
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
         <v>9453858.2677165363</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9489336.103851825</v>
       </c>
       <c r="F10" cm="1">
@@ -1024,8 +2405,61 @@
         <v>9489336.103851825</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f t="shared" si="3"/>
+        <v>1.218228683111293</v>
+      </c>
+      <c r="B11" cm="1">
+        <f t="array" ref="B11" xml:space="preserve"> FC_AMT * A11</f>
+        <v>9745829.4648903441</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>8712000</v>
+      </c>
+      <c r="D11">
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
+        <v>9453858.2677165363</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>9585829.4648903441</v>
+      </c>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11" xml:space="preserve"> FC_AMT * MAX(A11, K_CALL) - PREM_CALL * FC_AMT</f>
+        <v>9585829.4648903441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f t="shared" si="3"/>
+        <v>1.230410969942406</v>
+      </c>
+      <c r="B12" cm="1">
+        <f t="array" ref="B12" xml:space="preserve"> FC_AMT * A12</f>
+        <v>9843287.7595392484</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>8712000</v>
+      </c>
+      <c r="D12">
+        <f xml:space="preserve"> [0]!USD_mm_proceeds</f>
+        <v>9453858.2677165363</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>9683287.7595392484</v>
+      </c>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12" xml:space="preserve"> FC_AMT * MAX(A12, K_CALL) - PREM_CALL * FC_AMT</f>
+        <v>9683287.7595392484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1088,7 +2522,7 @@
       </c>
       <c r="B6" s="6">
         <f>MAX(Sensitivity!B2:B12)</f>
-        <v>9649336.103851825</v>
+        <v>9843287.7595392484</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
